--- a/data/trans_dic/P35-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P35-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico</t>
+          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico (tasa de respuesta: 97,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,17</t>
+          <t>3,12; 6,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 8,07</t>
+          <t>3,2; 7,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,28; 12,92</t>
+          <t>7,17; 12,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,48; 21,83</t>
+          <t>9,78; 21,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,04</t>
+          <t>3,61; 8,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,71; 17,53</t>
+          <t>10,58; 17,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,6; 14,75</t>
+          <t>8,65; 14,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,24; 34,66</t>
+          <t>21,41; 34,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,98</t>
+          <t>3,68; 6,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,52; 11,92</t>
+          <t>7,61; 11,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,7; 13,04</t>
+          <t>8,64; 13,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,24; 24,92</t>
+          <t>16,0; 24,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,66</t>
+          <t>2,56; 5,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,69; 16,14</t>
+          <t>10,86; 16,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,16; 15,66</t>
+          <t>10,1; 15,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,16; 29,96</t>
+          <t>19,9; 30,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 12,9</t>
+          <t>7,88; 13,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,48; 24,36</t>
+          <t>17,63; 24,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,93; 27,79</t>
+          <t>20,88; 28,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,01; 26,17</t>
+          <t>13,34; 26,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 8,28</t>
+          <t>5,54; 8,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,85; 19,03</t>
+          <t>14,8; 19,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,26; 20,55</t>
+          <t>16,31; 20,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,6; 26,37</t>
+          <t>17,08; 26,33</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 11,96</t>
+          <t>7,21; 11,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,36; 20,15</t>
+          <t>14,21; 20,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,53; 23,2</t>
+          <t>16,55; 23,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,82; 29,54</t>
+          <t>21,73; 29,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,32; 15,61</t>
+          <t>10,06; 15,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,77; 31,07</t>
+          <t>24,26; 30,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,95; 31,15</t>
+          <t>24,22; 31,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,67; 35,39</t>
+          <t>28,62; 35,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 13,03</t>
+          <t>9,54; 13,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,93; 24,8</t>
+          <t>20,01; 24,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,1; 25,91</t>
+          <t>21,6; 26,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,51; 31,58</t>
+          <t>26,39; 31,33</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,24; 17,43</t>
+          <t>11,22; 17,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,46; 28,7</t>
+          <t>21,23; 28,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,69; 35,55</t>
+          <t>27,54; 35,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,77; 35,38</t>
+          <t>10,5; 35,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,77; 23,03</t>
+          <t>16,05; 22,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,61; 38,82</t>
+          <t>30,59; 39,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,64; 38,89</t>
+          <t>31,47; 39,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,19; 39,13</t>
+          <t>30,98; 39,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,6; 19,34</t>
+          <t>14,55; 19,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,12; 32,67</t>
+          <t>26,72; 32,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,42; 36,11</t>
+          <t>30,5; 36,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,09; 35,97</t>
+          <t>18,3; 35,86</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,52; 41,04</t>
+          <t>31,52; 41,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,58; 52,37</t>
+          <t>41,82; 51,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,66; 45,63</t>
+          <t>35,97; 45,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39,79; 48,32</t>
+          <t>40,16; 48,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,19; 37,17</t>
+          <t>27,91; 36,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,21; 56,65</t>
+          <t>46,41; 56,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,74; 52,31</t>
+          <t>42,91; 52,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,13; 47,5</t>
+          <t>41,37; 47,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,26; 37,97</t>
+          <t>31,15; 37,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45,47; 52,79</t>
+          <t>45,58; 52,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40,74; 47,24</t>
+          <t>40,38; 47,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,79; 46,83</t>
+          <t>41,62; 46,76</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,2; 51,05</t>
+          <t>39,5; 51,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,94; 59,5</t>
+          <t>47,07; 58,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,24; 59,76</t>
+          <t>48,71; 59,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44,74; 53,67</t>
+          <t>44,93; 53,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,49; 52,17</t>
+          <t>41,87; 51,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,79; 62,54</t>
+          <t>51,52; 62,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,11; 63,32</t>
+          <t>52,88; 62,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,95; 48,39</t>
+          <t>12,37; 48,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41,95; 49,67</t>
+          <t>42,07; 49,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50,43; 58,89</t>
+          <t>51,21; 59,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52,83; 60,25</t>
+          <t>52,69; 60,26</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,02; 49,27</t>
+          <t>20,71; 49,26</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>45,63; 59,64</t>
+          <t>46,43; 59,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>48,98; 63,83</t>
+          <t>49,17; 62,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,86; 52,78</t>
+          <t>41,39; 52,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46,81; 56,27</t>
+          <t>46,39; 56,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,8; 53,08</t>
+          <t>40,9; 53,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,09; 56,5</t>
+          <t>45,87; 56,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,41; 52,41</t>
+          <t>41,55; 52,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,85; 52,45</t>
+          <t>45,7; 52,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45,14; 54,18</t>
+          <t>45,73; 54,58</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48,6; 57,42</t>
+          <t>49,07; 57,22</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42,83; 50,87</t>
+          <t>42,65; 51,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,12; 52,68</t>
+          <t>47,38; 52,95</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,12; 18,85</t>
+          <t>16,32; 18,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,29; 27,59</t>
+          <t>24,28; 27,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,19; 29,48</t>
+          <t>26,3; 29,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,92; 34,82</t>
+          <t>24,37; 34,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,04; 22,99</t>
+          <t>20,12; 22,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,68; 36,02</t>
+          <t>32,68; 36,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,12; 36,65</t>
+          <t>32,85; 36,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,54; 37,25</t>
+          <t>27,51; 37,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,67; 20,59</t>
+          <t>18,61; 20,49</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29,16; 31,54</t>
+          <t>29,24; 31,39</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30,3; 32,64</t>
+          <t>30,31; 32,56</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,57; 35,27</t>
+          <t>28,79; 35,56</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico</t>
+          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico (tasa de respuesta: 97,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14118; 33712</t>
+          <t>14681; 32774</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15379; 35513</t>
+          <t>14066; 33276</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29710; 52742</t>
+          <t>29274; 53058</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37938; 87308</t>
+          <t>39103; 85365</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15828; 35695</t>
+          <t>16031; 36471</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44696; 73143</t>
+          <t>44160; 71983</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33482; 57447</t>
+          <t>33689; 57774</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>66512; 108563</t>
+          <t>67065; 106732</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34347; 63766</t>
+          <t>33677; 59974</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64499; 102232</t>
+          <t>65236; 98828</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69402; 104045</t>
+          <t>68963; 104122</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>115806; 177698</t>
+          <t>114112; 177179</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18430; 39741</t>
+          <t>17982; 39503</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71256; 107563</t>
+          <t>72386; 109004</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59200; 91235</t>
+          <t>58853; 92518</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81159; 126902</t>
+          <t>84280; 130946</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45721; 75865</t>
+          <t>46362; 76721</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>103473; 144227</t>
+          <t>104410; 144389</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>116843; 155081</t>
+          <t>116518; 157299</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66543; 133874</t>
+          <t>68249; 134268</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70805; 106821</t>
+          <t>71415; 107676</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>186965; 239514</t>
+          <t>186355; 242020</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>185541; 234395</t>
+          <t>186073; 236374</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>164566; 246616</t>
+          <t>159719; 246246</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43562; 73297</t>
+          <t>44185; 73474</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94004; 131904</t>
+          <t>93020; 132348</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>108856; 152788</t>
+          <t>109022; 151834</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117026; 158439</t>
+          <t>116566; 158081</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67296; 101752</t>
+          <t>65576; 103381</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>164604; 215168</t>
+          <t>167985; 212894</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>155920; 202792</t>
+          <t>157660; 202703</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>155182; 191524</t>
+          <t>154871; 190245</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>118968; 164774</t>
+          <t>120600; 167741</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>268491; 334038</t>
+          <t>269479; 331166</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>276362; 339229</t>
+          <t>282821; 343880</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>285609; 340272</t>
+          <t>284331; 337630</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54878; 85091</t>
+          <t>54747; 86047</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>128599; 172015</t>
+          <t>127237; 172767</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177476; 227830</t>
+          <t>176519; 225541</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95596; 314067</t>
+          <t>93237; 313578</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>77182; 112739</t>
+          <t>78554; 112374</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>183210; 232347</t>
+          <t>183074; 234078</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>202353; 248736</t>
+          <t>201292; 252519</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>214904; 278537</t>
+          <t>220505; 281043</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>142752; 189067</t>
+          <t>142236; 189275</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>324808; 391350</t>
+          <t>320048; 386557</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>389480; 462373</t>
+          <t>390572; 461778</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>273326; 575281</t>
+          <t>292745; 573570</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>115782; 150731</t>
+          <t>115797; 152033</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>175489; 220991</t>
+          <t>176492; 217024</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>168642; 215783</t>
+          <t>170108; 214163</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>223340; 271196</t>
+          <t>225386; 269493</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>110785; 146070</t>
+          <t>109656; 144508</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>198760; 243705</t>
+          <t>199643; 244146</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>209576; 256539</t>
+          <t>210423; 259269</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>224264; 258977</t>
+          <t>225565; 258746</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>237659; 288682</t>
+          <t>236839; 287976</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>387476; 449849</t>
+          <t>388408; 446892</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>392403; 455024</t>
+          <t>388954; 454671</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>462373; 518117</t>
+          <t>460538; 517400</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>111086; 144650</t>
+          <t>111920; 146076</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>142601; 180743</t>
+          <t>142974; 178761</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>157286; 194859</t>
+          <t>158834; 194411</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>164732; 197585</t>
+          <t>165421; 197170</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>134025; 168551</t>
+          <t>135279; 167657</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>177848; 214730</t>
+          <t>176902; 212955</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>195781; 233437</t>
+          <t>194951; 231889</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>78699; 294108</t>
+          <t>75158; 293742</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>254375; 301235</t>
+          <t>255134; 302338</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>326352; 381097</t>
+          <t>331420; 383202</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>367026; 418553</t>
+          <t>366067; 418645</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>205141; 480898</t>
+          <t>202107; 480806</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>92787; 121291</t>
+          <t>94415; 121760</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118192; 154022</t>
+          <t>118648; 150672</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>104683; 131989</t>
+          <t>103506; 131465</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>132356; 159116</t>
+          <t>131169; 159121</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>130014; 169128</t>
+          <t>130313; 169313</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>174303; 213672</t>
+          <t>173452; 212978</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>165167; 209035</t>
+          <t>165707; 209071</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>195053; 223156</t>
+          <t>194426; 223315</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>235633; 282818</t>
+          <t>238709; 284903</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>301087; 355726</t>
+          <t>303960; 354439</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>277926; 330130</t>
+          <t>276737; 332782</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>333730; 373088</t>
+          <t>335508; 374950</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>504055; 589433</t>
+          <t>510422; 590682</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>808315; 918082</t>
+          <t>808044; 923851</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>874749; 984567</t>
+          <t>878132; 981053</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>862249; 1204823</t>
+          <t>843324; 1198696</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>643049; 737446</t>
+          <t>645355; 734471</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1128156; 1243553</t>
+          <t>1128096; 1245567</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1157730; 1281273</t>
+          <t>1148481; 1268184</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1043356; 1361965</t>
+          <t>1005768; 1371118</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1182969; 1304283</t>
+          <t>1178787; 1297968</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1976645; 2138551</t>
+          <t>1982308; 2128182</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2070915; 2231270</t>
+          <t>2071546; 2225499</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2032995; 2509442</t>
+          <t>2048831; 2530350</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P35-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P35-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,97</t>
+          <t>3,09; 7,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,56</t>
+          <t>3,55; 7,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,17; 12,99</t>
+          <t>7,03; 13,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,78; 21,34</t>
+          <t>11,38; 23,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,22</t>
+          <t>3,61; 7,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 17,25</t>
+          <t>10,69; 17,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,65; 14,83</t>
+          <t>8,67; 14,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,41; 34,08</t>
+          <t>21,38; 34,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,56</t>
+          <t>3,76; 6,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 11,53</t>
+          <t>7,69; 11,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,64; 13,05</t>
+          <t>8,7; 12,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,0; 24,84</t>
+          <t>17,6; 25,74</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,63</t>
+          <t>2,72; 5,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 16,35</t>
+          <t>10,5; 15,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,1; 15,88</t>
+          <t>10,29; 15,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,9; 30,92</t>
+          <t>20,52; 31,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,88; 13,04</t>
+          <t>7,86; 13,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,63; 24,39</t>
+          <t>17,33; 24,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,88; 28,18</t>
+          <t>20,88; 28,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,34; 26,25</t>
+          <t>20,6; 28,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 8,35</t>
+          <t>5,56; 8,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,8; 19,23</t>
+          <t>14,8; 19,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,31; 20,72</t>
+          <t>16,37; 20,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 26,33</t>
+          <t>22,02; 28,32</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 11,99</t>
+          <t>7,24; 12,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,21; 20,22</t>
+          <t>14,27; 20,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,55; 23,06</t>
+          <t>16,7; 23,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,73; 29,47</t>
+          <t>22,05; 29,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,06; 15,86</t>
+          <t>10,35; 15,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,26; 30,74</t>
+          <t>23,95; 30,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,22; 31,14</t>
+          <t>24,22; 30,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,62; 35,15</t>
+          <t>29,13; 35,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,54; 13,26</t>
+          <t>9,49; 12,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,01; 24,59</t>
+          <t>20,19; 24,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,6; 26,26</t>
+          <t>21,29; 25,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,39; 31,33</t>
+          <t>26,92; 31,63</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,22; 17,63</t>
+          <t>11,23; 17,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,23; 28,83</t>
+          <t>21,26; 28,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,54; 35,19</t>
+          <t>27,54; 35,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,5; 35,32</t>
+          <t>30,73; 38,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,05; 22,96</t>
+          <t>16,11; 23,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,59; 39,11</t>
+          <t>30,74; 38,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,47; 39,48</t>
+          <t>31,52; 38,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,98; 39,49</t>
+          <t>34,97; 40,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,55; 19,36</t>
+          <t>14,54; 19,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,72; 32,27</t>
+          <t>27,11; 32,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,5; 36,06</t>
+          <t>30,53; 35,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,3; 35,86</t>
+          <t>34,06; 38,36</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,52; 41,39</t>
+          <t>31,56; 41,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,82; 51,43</t>
+          <t>41,66; 51,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,97; 45,29</t>
+          <t>35,31; 45,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,16; 48,02</t>
+          <t>40,3; 47,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,91; 36,78</t>
+          <t>28,22; 37,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,41; 56,76</t>
+          <t>46,24; 57,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,91; 52,87</t>
+          <t>42,8; 52,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,37; 47,46</t>
+          <t>41,22; 48,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,15; 37,88</t>
+          <t>30,71; 37,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45,58; 52,44</t>
+          <t>45,67; 52,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40,38; 47,2</t>
+          <t>40,6; 47,3</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,62; 46,76</t>
+          <t>41,84; 46,88</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,5; 51,55</t>
+          <t>39,16; 51,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47,07; 58,85</t>
+          <t>46,57; 58,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,71; 59,62</t>
+          <t>48,85; 59,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44,93; 53,55</t>
+          <t>44,11; 52,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,87; 51,9</t>
+          <t>41,48; 52,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,52; 62,02</t>
+          <t>51,62; 62,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,88; 62,9</t>
+          <t>52,6; 63,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,37; 48,33</t>
+          <t>44,7; 51,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42,07; 49,85</t>
+          <t>42,14; 49,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51,21; 59,21</t>
+          <t>51,09; 58,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52,69; 60,26</t>
+          <t>52,63; 60,43</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,71; 49,26</t>
+          <t>45,96; 51,45</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,43; 59,88</t>
+          <t>46,49; 60,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49,17; 62,44</t>
+          <t>48,27; 62,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,39; 52,57</t>
+          <t>40,5; 52,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46,39; 56,27</t>
+          <t>46,63; 55,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,9; 53,14</t>
+          <t>41,47; 53,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,87; 56,32</t>
+          <t>46,06; 56,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,55; 52,42</t>
+          <t>41,11; 52,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,7; 52,49</t>
+          <t>46,21; 52,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45,73; 54,58</t>
+          <t>45,01; 53,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49,07; 57,22</t>
+          <t>48,93; 57,41</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42,65; 51,28</t>
+          <t>42,52; 50,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,38; 52,95</t>
+          <t>47,1; 52,9</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,32; 18,89</t>
+          <t>16,28; 18,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,28; 27,76</t>
+          <t>24,29; 27,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,3; 29,38</t>
+          <t>26,35; 29,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,37; 34,65</t>
+          <t>32,68; 36,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,12; 22,89</t>
+          <t>20,18; 23,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,68; 36,08</t>
+          <t>32,8; 36,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,85; 36,28</t>
+          <t>33,29; 36,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>27,51; 37,5</t>
+          <t>36,56; 39,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,61; 20,49</t>
+          <t>18,61; 20,5</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29,24; 31,39</t>
+          <t>29,17; 31,43</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30,31; 32,56</t>
+          <t>30,37; 32,66</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,79; 35,56</t>
+          <t>35,18; 37,41</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59049</t>
+          <t>65849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85536</t>
+          <t>99914</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>144585</t>
+          <t>165763</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14681; 32774</t>
+          <t>14551; 34381</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14066; 33276</t>
+          <t>15621; 33888</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29274; 53058</t>
+          <t>28708; 53678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39103; 85365</t>
+          <t>46422; 94754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16031; 36471</t>
+          <t>16002; 34805</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44160; 71983</t>
+          <t>44595; 72240</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33689; 57774</t>
+          <t>33749; 57225</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67065; 106732</t>
+          <t>77501; 126450</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33677; 59974</t>
+          <t>34382; 60258</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65236; 98828</t>
+          <t>65904; 98969</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68963; 104122</t>
+          <t>69422; 102868</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>114112; 177179</t>
+          <t>135536; 198308</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103680</t>
+          <t>120224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>108441</t>
+          <t>123178</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>212121</t>
+          <t>243402</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17982; 39503</t>
+          <t>19072; 39185</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72386; 109004</t>
+          <t>69995; 106428</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58853; 92518</t>
+          <t>59981; 91944</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84280; 130946</t>
+          <t>97835; 148324</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46362; 76721</t>
+          <t>46241; 76560</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>104410; 144389</t>
+          <t>102597; 145880</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>116518; 157299</t>
+          <t>116556; 156595</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>68249; 134268</t>
+          <t>103222; 143027</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71415; 107676</t>
+          <t>71738; 106246</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>186355; 242020</t>
+          <t>186246; 239951</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>186073; 236374</t>
+          <t>186773; 238452</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>159719; 246246</t>
+          <t>215316; 276981</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>137714</t>
+          <t>161440</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>173287</t>
+          <t>201472</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>311001</t>
+          <t>362912</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44185; 73474</t>
+          <t>44371; 74899</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93020; 132348</t>
+          <t>93387; 134448</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109022; 151834</t>
+          <t>109962; 152003</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116566; 158081</t>
+          <t>136906; 183326</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>65576; 103381</t>
+          <t>67511; 102399</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>167985; 212894</t>
+          <t>165861; 214013</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>157660; 202703</t>
+          <t>157650; 201756</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>154871; 190245</t>
+          <t>180855; 221086</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120600; 167741</t>
+          <t>120006; 164312</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>269479; 331166</t>
+          <t>271991; 335157</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>282821; 343880</t>
+          <t>278774; 340311</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>284331; 337630</t>
+          <t>334248; 392703</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217352</t>
+          <t>241331</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>254987</t>
+          <t>276711</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>472339</t>
+          <t>518042</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54747; 86047</t>
+          <t>54822; 86890</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>127237; 172767</t>
+          <t>127404; 172993</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>176519; 225541</t>
+          <t>176472; 224323</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93237; 313578</t>
+          <t>215314; 266496</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>78554; 112374</t>
+          <t>78842; 113941</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>183074; 234078</t>
+          <t>183965; 232940</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>201292; 252519</t>
+          <t>201558; 249131</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>220505; 281043</t>
+          <t>257329; 297048</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>142236; 189275</t>
+          <t>142103; 188632</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>320048; 386557</t>
+          <t>324666; 391216</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>390572; 461778</t>
+          <t>390882; 460634</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>292745; 573570</t>
+          <t>489177; 550945</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>246941</t>
+          <t>268580</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>241683</t>
+          <t>271820</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>488625</t>
+          <t>540400</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>115797; 152033</t>
+          <t>115931; 152629</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>176492; 217024</t>
+          <t>175790; 218657</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170108; 214163</t>
+          <t>166956; 213025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>225386; 269493</t>
+          <t>245588; 291634</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>109656; 144508</t>
+          <t>110882; 148972</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>199643; 244146</t>
+          <t>198907; 245478</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>210423; 259269</t>
+          <t>209884; 256099</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>225565; 258746</t>
+          <t>250528; 292193</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>236839; 287976</t>
+          <t>233448; 288484</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>388408; 446892</t>
+          <t>389208; 449008</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>388954; 454671</t>
+          <t>391096; 455650</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>460538; 517400</t>
+          <t>509226; 570637</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181257</t>
+          <t>197862</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>191124</t>
+          <t>210440</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>372382</t>
+          <t>408302</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>111920; 146076</t>
+          <t>110978; 145263</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>142974; 178761</t>
+          <t>141472; 177290</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>158834; 194411</t>
+          <t>159295; 194104</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>165421; 197170</t>
+          <t>179569; 214987</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>135279; 167657</t>
+          <t>134018; 168650</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>176902; 212955</t>
+          <t>177241; 212982</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>194951; 231889</t>
+          <t>193931; 232616</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>75158; 293742</t>
+          <t>196055; 227427</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>255134; 302338</t>
+          <t>255530; 302526</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>331420; 383202</t>
+          <t>330618; 381302</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>366067; 418645</t>
+          <t>365606; 419814</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>202107; 480806</t>
+          <t>388632; 435039</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>145668</t>
+          <t>159284</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>208576</t>
+          <t>229576</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>354244</t>
+          <t>388860</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>94415; 121760</t>
+          <t>94549; 122210</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118648; 150672</t>
+          <t>116488; 150826</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>103506; 131465</t>
+          <t>101280; 131236</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>131169; 159121</t>
+          <t>144645; 173463</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>130313; 169313</t>
+          <t>132147; 171621</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>173452; 212978</t>
+          <t>174185; 213748</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>165707; 209071</t>
+          <t>163942; 209458</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>194426; 223315</t>
+          <t>214516; 243778</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>238709; 284903</t>
+          <t>234971; 281577</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>303960; 354439</t>
+          <t>303092; 355646</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>276737; 332782</t>
+          <t>275905; 330809</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>335508; 374950</t>
+          <t>364716; 409634</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1091663</t>
+          <t>1214570</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1263634</t>
+          <t>1413111</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2355296</t>
+          <t>2627681</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>510422; 590682</t>
+          <t>508961; 587680</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>808044; 923851</t>
+          <t>808272; 912678</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>878132; 981053</t>
+          <t>879891; 986707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>843324; 1198696</t>
+          <t>1154652; 1279714</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>645355; 734471</t>
+          <t>647402; 744599</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1128096; 1245567</t>
+          <t>1132348; 1251401</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1148481; 1268184</t>
+          <t>1163670; 1273608</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1005768; 1371118</t>
+          <t>1363945; 1468276</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1178787; 1297968</t>
+          <t>1179306; 1298809</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1982308; 2128182</t>
+          <t>1977435; 2130614</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2071546; 2225499</t>
+          <t>2076240; 2232777</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2048831; 2530350</t>
+          <t>2555255; 2717022</t>
         </is>
       </c>
     </row>
